--- a/data/trans_bre/IP16B98-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16B98-Edad-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 0,0</t>
+          <t>-49,09; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 87,7</t>
+          <t>-13,85; 87,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 0,0</t>
+          <t>-49,09; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,09; —</t>
+          <t>-24,81; —</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,31; 18,19</t>
+          <t>-45,07; 17,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,0; 22,01</t>
+          <t>-50,19; 21,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,56</t>
+          <t>0,0; 66,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 217,95</t>
+          <t>0,0; 201,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 16,2</t>
+          <t>-11,01; 16,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 17,21</t>
+          <t>-3,73; 16,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 19,87</t>
+          <t>-11,43; 20,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 21,45</t>
+          <t>-4,01; 20,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B98-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16B98-Edad-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 0,0</t>
+          <t>-48,66; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 87,35</t>
+          <t>-13,31; 87,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 0,0</t>
+          <t>-48,66; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,81; —</t>
+          <t>-18,13; —</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,07; 17,52</t>
+          <t>-43,67; 17,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,19; 21,09</t>
+          <t>-49,08; 21,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,88</t>
+          <t>0,0; 67,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 201,87</t>
+          <t>0,0; 202,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 16,41</t>
+          <t>-12,83; 14,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 16,81</t>
+          <t>-4,58; 16,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 20,33</t>
+          <t>-13,96; 17,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 20,64</t>
+          <t>-4,7; 20,41</t>
         </is>
       </c>
     </row>
